--- a/artfynd/S 2213-2025 artfynd.xlsx
+++ b/artfynd/S 2213-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4544,48 +4544,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>81142558</v>
+        <v>137542853</v>
       </c>
       <c r="B39" t="n">
-        <v>97983</v>
+        <v>99438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storåsen, Jmt</t>
+          <t>Klingertjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557854</v>
+        <v>558146</v>
       </c>
       <c r="R39" t="n">
-        <v>6968810</v>
+        <v>6968983</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4609,12 +4618,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2019-10-21</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2019-10-21</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4629,73 +4648,65 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81142558</t>
+          <t>https://artportalen.se/Sighting/137542853</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127653316</v>
+        <v>81142558</v>
       </c>
       <c r="B40" t="n">
-        <v>56689</v>
+        <v>97983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>206046</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stor Gallberget, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555378</v>
+        <v>557854</v>
       </c>
       <c r="R40" t="n">
-        <v>6965034</v>
+        <v>6968810</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4719,17 +4730,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2019-10-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ko med kalv. Kalven mycket ung, kanske 2-3 veckor.</t>
+          <t>2019-10-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4744,16 +4750,131 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Andreas Öster, Andrea Albeck, Malte Lindberg, Lukas Stenbäck, Alexander Singer, Cecilia Öster, Martin Westberg, Erica Hästdahl, Teresa Jonsson, Johan Råghall, Lina Lejonberg, Ola Hammarström, Nicklas Gustavsson, Rashid Kadhim</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142558</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127653316</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stor Gallberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>555378</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6965034</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ko med kalv. Kalven mycket ung, kanske 2-3 veckor.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Andrea Albeck, Malte Lindberg, Lukas Stenbäck, Alexander Singer, Cecilia Öster, Martin Westberg, Erica Hästdahl, Teresa Jonsson, Johan Råghall, Lina Lejonberg, Ola Hammarström, Nicklas Gustavsson, Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127653316</t>
         </is>
@@ -4800,6 +4921,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
